--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0191.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0191.xlsx
@@ -31189,7 +31189,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Nhìn con Hornett to thế kia! Ta chưa bao giờ thấy tận mắt bao giờ!</t>
+          <t>Nhìn con Hornett to thế kia! Tao chưa bao giờ thấy tận mắt bao giờ!</t>
         </is>
       </c>
     </row>
@@ -32749,7 +32749,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Bao nhiêu lần ta phải nhắc cô rồi, Martina? Vinh quang của cuộc săn thuộc về Quý bà Valeria, Anh Hùng của các Anh Hùng. Và danh dự của gia tộc chúng ta.</t>
+          <t>Bao nhiêu lần tao phải nhắc cô rồi, Martina? Vinh quang của cuộc săn thuộc về Quý bà Valeria, Anh Hùng của các Anh Hùng. Và danh dự của gia tộc chúng ta.</t>
         </is>
       </c>
     </row>
